--- a/fias_loader/X_DOC/as_param_type.xlsx
+++ b/fias_loader/X_DOC/as_param_type.xlsx
@@ -222,6 +222,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -239,7 +240,7 @@
       <family val="0"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -255,7 +256,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF87D1D1"/>
-        <bgColor rgb="FFC0C0C0"/>
+        <bgColor rgb="FF8CCFB7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8CCFB7"/>
+        <bgColor rgb="FF87D1D1"/>
       </patternFill>
     </fill>
   </fills>
@@ -293,7 +300,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -322,6 +329,18 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="false"/>
@@ -347,7 +366,7 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF8CCFB7"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
@@ -405,7 +424,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7.41"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="36.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="67.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="67.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10.46"/>
@@ -903,7 +922,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.52"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="6" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="70.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="70.04"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="5" style="0" width="11.52"/>
   </cols>
   <sheetData>
@@ -977,59 +996,59 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+    <row r="6" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="n">
         <v>324754</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+    <row r="7" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="n">
         <v>299415</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+    <row r="8" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="n">
         <v>341735</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+    <row r="9" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="n">
         <v>31145</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="8" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1078,7 +1097,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Обычный"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Страница &amp;P</oddFooter>
